--- a/babyopm_testing_overview.xlsx
+++ b/babyopm_testing_overview.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/b.pomiechowska@bham.ac.uk/Documents/GitHub/babypyopm/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C03FCA5D-B9E7-7347-8FDB-CAF17FC64F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E3536E-BD69-4540-8710-38D651172AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17380" xr2:uid="{2B0B869B-EEF1-F84F-986F-88A4D57F9EF3}"/>
+    <workbookView xWindow="1120" yWindow="780" windowWidth="28040" windowHeight="17380" xr2:uid="{2B0B869B-EEF1-F84F-986F-88A4D57F9EF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -327,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -359,9 +359,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -374,17 +371,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -762,7 +753,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="20" t="s">
         <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -799,147 +790,147 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21">
+      <c r="A3" s="18">
         <v>1499</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="18">
         <v>2078</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="19">
         <v>45857</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="21" t="s">
+      <c r="G3" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21">
+      <c r="A4" s="18">
         <v>1503</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="18">
         <v>2069</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="19">
         <v>45856</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="21" t="s">
+      <c r="G4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="18" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="18">
+      <c r="A5" s="16">
         <v>1513</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="16">
         <v>2145</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="17">
         <v>45891</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="16" t="s">
+      <c r="G5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
+      <c r="A6" s="16">
         <v>1540</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="16">
         <v>2152</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="17">
         <v>45891</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="16" t="s">
+      <c r="G6" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="15" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
+      <c r="A7" s="16">
         <v>1543</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="16">
         <v>2153</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="17">
         <v>45892</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="16" t="s">
+      <c r="G7" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="15" t="s">
         <v>45</v>
       </c>
     </row>
@@ -965,7 +956,7 @@
       <c r="G8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -994,7 +985,7 @@
       <c r="G9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -1019,7 +1010,7 @@
       <c r="G10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I10" s="3" t="s">
@@ -1048,7 +1039,7 @@
       <c r="G11" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I11" s="3" t="s">
@@ -1077,7 +1068,7 @@
       <c r="G12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -1117,10 +1108,10 @@
       <c r="G14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1146,10 +1137,10 @@
       <c r="G15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="11" t="s">
+      <c r="H15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1175,10 +1166,10 @@
       <c r="G16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I16" s="11" t="s">
+      <c r="H16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1204,10 +1195,10 @@
       <c r="G17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="11" t="s">
+      <c r="H17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1233,118 +1224,118 @@
       <c r="G18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H18" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I18" s="11" t="s">
+      <c r="H18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="12">
+      <c r="A19" s="11">
         <v>1859</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>2686</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13" t="s">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="13">
         <v>45744</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="16" t="s">
+      <c r="G19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="13">
+      <c r="A20" s="12">
         <v>1688</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <v>2618</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="13" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="13">
         <v>45744</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="16" t="s">
+      <c r="G20" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="12">
+      <c r="A21" s="11">
         <v>1858</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>2687</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="13" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="13">
         <v>45745</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="16" t="s">
+      <c r="G21" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="12" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13">
+      <c r="A22" s="12">
         <v>1853</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="12">
         <v>2674</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="14"/>
+      <c r="D22" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="13">
         <v>45748</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="16" t="s">
+      <c r="G22" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="12" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1368,10 +1359,10 @@
       <c r="G23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="H23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="3" t="s">
         <v>48</v>
       </c>
     </row>
